--- a/References.xlsx
+++ b/References.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="DieseArbeitsmappe"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12222" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12180" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Import" sheetId="30" r:id="rId1"/>
@@ -3776,8 +3776,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23764875" y="38100"/>
-          <a:ext cx="1253490" cy="419100"/>
+          <a:off x="22507575" y="38100"/>
+          <a:ext cx="1209675" cy="419100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4069,23 +4069,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I507"/>
-  <sheetFormatPr defaultColWidth="11.4324324324324" defaultRowHeight="14.55"/>
+  <sheetFormatPr defaultColWidth="11.4285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="65.8558558558559" customWidth="1"/>
-    <col min="2" max="2" width="31.7117117117117" customWidth="1"/>
-    <col min="3" max="3" width="9.85585585585586" customWidth="1"/>
-    <col min="4" max="4" width="15.1441441441441" customWidth="1"/>
-    <col min="5" max="5" width="32.2882882882883" customWidth="1"/>
-    <col min="6" max="6" width="95.4324324324324" customWidth="1"/>
-    <col min="8" max="8" width="17.2882882882883" customWidth="1"/>
-    <col min="9" max="9" width="30.2882882882883" customWidth="1"/>
-    <col min="12" max="12" width="26.8558558558559" customWidth="1"/>
-    <col min="13" max="13" width="22.4324324324324" customWidth="1"/>
-    <col min="14" max="14" width="12.2882882882883" customWidth="1"/>
-    <col min="15" max="15" width="39.7117117117117" customWidth="1"/>
-    <col min="16" max="16" width="34.1441441441441" customWidth="1"/>
-    <col min="17" max="17" width="65.7117117117117" customWidth="1"/>
-    <col min="18" max="18" width="126.288288288288" customWidth="1"/>
+    <col min="1" max="1" width="65.8571428571429" customWidth="1"/>
+    <col min="2" max="2" width="31.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="9.85714285714286" customWidth="1"/>
+    <col min="4" max="4" width="15.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="32.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="95.4285714285714" customWidth="1"/>
+    <col min="8" max="8" width="17.2857142857143" customWidth="1"/>
+    <col min="9" max="9" width="30.2857142857143" customWidth="1"/>
+    <col min="12" max="12" width="26.8571428571429" customWidth="1"/>
+    <col min="13" max="13" width="22.4285714285714" customWidth="1"/>
+    <col min="14" max="14" width="12.2857142857143" customWidth="1"/>
+    <col min="15" max="15" width="39.7142857142857" customWidth="1"/>
+    <col min="16" max="16" width="34.1428571428571" customWidth="1"/>
+    <col min="17" max="17" width="65.7142857142857" customWidth="1"/>
+    <col min="18" max="18" width="126.285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9">
@@ -20265,19 +20265,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M507"/>
-  <sheetFormatPr defaultColWidth="11.4324324324324" defaultRowHeight="14.55"/>
+  <sheetFormatPr defaultColWidth="11.4285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="65.8558558558559" customWidth="1"/>
-    <col min="2" max="2" width="31.7117117117117" customWidth="1"/>
-    <col min="3" max="3" width="9.85585585585586" customWidth="1"/>
-    <col min="4" max="4" width="15.1441441441441" customWidth="1"/>
-    <col min="5" max="5" width="52.8558558558559" customWidth="1"/>
-    <col min="6" max="6" width="95.4324324324324" customWidth="1"/>
-    <col min="8" max="8" width="17.2882882882883" customWidth="1"/>
-    <col min="9" max="9" width="30.2882882882883" customWidth="1"/>
-    <col min="10" max="10" width="11.4324324324324" style="8"/>
-    <col min="11" max="12" width="77.7117117117117" style="9" customWidth="1"/>
-    <col min="13" max="13" width="126.288288288288" customWidth="1"/>
+    <col min="1" max="1" width="65.8571428571429" customWidth="1"/>
+    <col min="2" max="2" width="31.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="9.85714285714286" customWidth="1"/>
+    <col min="4" max="4" width="15.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="52.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="95.4285714285714" customWidth="1"/>
+    <col min="8" max="8" width="17.2857142857143" customWidth="1"/>
+    <col min="9" max="9" width="30.2857142857143" customWidth="1"/>
+    <col min="10" max="10" width="11.4285714285714" style="8"/>
+    <col min="11" max="12" width="77.7142857142857" style="9" customWidth="1"/>
+    <col min="13" max="13" width="126.285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:13">
@@ -37254,11 +37254,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="11.4324324324324" defaultRowHeight="14.55" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="11.4285714285714" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="88.8558558558559" customWidth="1"/>
-    <col min="2" max="2" width="68.7117117117117" customWidth="1"/>
-    <col min="3" max="3" width="27.1441441441441" customWidth="1"/>
+    <col min="1" max="1" width="88.8571428571429" customWidth="1"/>
+    <col min="2" max="2" width="68.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="27.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="47.25" customHeight="1" spans="1:2">

--- a/References.xlsx
+++ b/References.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="253">
   <si>
     <t>@article{example2024,   title = {A Reference Example},   journal = {Journal of Examples},   publisher = {Example Press},   author = {Doe, Jane},   year = {2024},   month = aug,   pages = {185–209} }</t>
   </si>
@@ -2496,6 +2496,23 @@
     <t>Ja</t>
   </si>
   <si>
+    <t>@book{Cohen1988,
+  author = {Cohen, Jacob},
+  title = {Statistical power analysis for the behavioral sciences},
+  edition = {2},
+  publisher = {Lawrence Erlbaum Associates},
+  address = {Hillsdale, NJ},
+  year = {1988},
+  isbn = {0805802835}
+}</t>
+  </si>
+  <si>
+    <t>statistik</t>
+  </si>
+  <si>
+    <t>https://ennosgermancourse-my.sharepoint.com/:b:/r/personal/enno_winkler_spb-ew_de/Documents/Lehre%20%20So%20Se2026/Modul-08-006-0007/Literatur/CohenPower.pdf?csf=1&amp;web=1&amp;e=IJbnrE</t>
+  </si>
+  <si>
     <t>Bibtex templates</t>
   </si>
   <si>
@@ -26085,37 +26102,47 @@
         <v>206</v>
       </c>
     </row>
-    <row r="159" ht="36" customHeight="1" spans="1:9">
-      <c r="A159" s="16"/>
+    <row r="159" ht="36" customHeight="1" spans="1:11">
+      <c r="A159" s="16" t="s">
+        <v>207</v>
+      </c>
       <c r="B159" s="17" t="str">
         <f t="shared" si="26"/>
-        <v/>
+        <v>@Cohen1988</v>
       </c>
       <c r="C159" s="18" t="str">
         <f t="shared" si="27"/>
-        <v>[]</v>
+        <v>[@Cohen1988]</v>
       </c>
       <c r="D159" s="19" t="str">
         <f t="shared" si="28"/>
-        <v/>
+        <v>1988</v>
       </c>
       <c r="E159" s="19" t="str">
         <f t="shared" si="29"/>
-        <v/>
+        <v>Cohen, Jacob</v>
       </c>
       <c r="F159" s="20" t="str">
         <f t="shared" si="30"/>
-        <v/>
+        <v>Statistical power analysis for the behavioral sciences</v>
       </c>
       <c r="G159" s="21" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="H159" s="22" t="str">
+      <c r="H159" s="22">
         <f ca="1" t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="I159" s="34"/>
+        <v>46097.4688194444</v>
+      </c>
+      <c r="I159" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="J159" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="K159" s="9" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="160" ht="36" customHeight="1" spans="1:9">
       <c r="A160" s="16"/>
@@ -37241,6 +37268,7 @@
     <hyperlink ref="J17" r:id="rId29" display="https://ennosgermancourse-my.sharepoint.com/:b:/r/personal/enno_winkler_spb-ew_de/Documents/A%20Fernstudium%20Kursmaterial/Bachelorarbeit/Info/LIT/Determinants%20of%20physical%20activity%20maintenance%20a%20systematic%20review%20and%20meta-analyses.pdf?csf=1&amp;web=1&amp;e=Jjhfg9"/>
     <hyperlink ref="J4" r:id="rId30" display="https://ennosgermancourse-my.sharepoint.com/:b:/r/personal/enno_winkler_spb-ew_de/Documents/Lehre%20%20So%20Se2026/Modul-08-006-0007/Literatur/What%20works%20healthy%20eating%20and%20activity%20community%20based.pdf?csf=1&amp;web=1&amp;e=sCzZfE"/>
     <hyperlink ref="J158" r:id="rId31" display="https://ennosgermancourse-my.sharepoint.com/:b:/r/personal/enno_winkler_spb-ew_de/Documents/Lehre%20%20So%20Se2026/Modul-08-006-0007/Literatur/Svendsen2022selfBACK.pdf?csf=1&amp;web=1&amp;e=cCrbwL"/>
+    <hyperlink ref="J159" r:id="rId32" display="https://ennosgermancourse-my.sharepoint.com/:b:/r/personal/enno_winkler_spb-ew_de/Documents/Lehre%20%20So%20Se2026/Modul-08-006-0007/Literatur/CohenPower.pdf?csf=1&amp;web=1&amp;e=IJbnrE"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -37263,176 +37291,176 @@
   <sheetData>
     <row r="1" ht="47.25" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="72.75" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" ht="180" customHeight="1" spans="1:2">
       <c r="A5" s="7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" ht="210" customHeight="1" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" ht="210" customHeight="1" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" ht="255" customHeight="1" spans="1:2">
       <c r="A9" s="7" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" ht="255" customHeight="1" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" ht="285" customHeight="1" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" ht="285" customHeight="1" spans="1:2">
       <c r="A12" s="7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" ht="255" customHeight="1" spans="1:2">
       <c r="A13" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" ht="165" customHeight="1" spans="1:2">
       <c r="A14" s="7" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" ht="165" customHeight="1" spans="1:2">
       <c r="A15" s="7" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" ht="165" customHeight="1" spans="1:2">
       <c r="A16" s="7" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" ht="225" customHeight="1" spans="1:2">
       <c r="A17" s="7" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" ht="180" customHeight="1" spans="1:2">
       <c r="A18" s="7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" ht="105" customHeight="1" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" ht="120" customHeight="1" spans="1:2">
       <c r="A20" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" ht="135" customHeight="1" spans="1:1">
       <c r="A21" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/References.xlsx
+++ b/References.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="DieseArbeitsmappe"/>
   <bookViews>
-    <workbookView windowWidth="14880" windowHeight="11655" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12180" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Import" sheetId="30" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="278">
   <si>
     <t>@article{example2024,   title = {A Reference Example},   journal = {Journal of Examples},   publisher = {Example Press},   author = {Doe, Jane},   year = {2024},   month = aug,   pages = {185–209} }</t>
   </si>
@@ -2781,6 +2781,21 @@
 </t>
   </si>
   <si>
+    <t>@incollection{HagerHasselhorn2000,
+  author    = {Hager, Willi and Hasselhorn, Marcus},
+  title     = {{Psychologische Interventionsmaßnahmen: Was sollen sie bewirken können?}},
+  booktitle = {{Evaluation psychologischer Interventionsmaßnahmen}},
+  editor    = {Hager, Willi and Patry, Jean-Luc and Brezing, Hermann},
+  year      = {2000},
+  pages     = {41--85},
+  publisher = {Huber},
+  address   = {Bern}
+}</t>
+  </si>
+  <si>
+    <t>definition</t>
+  </si>
+  <si>
     <t>Bibtex templates</t>
   </si>
   <si>
@@ -26958,14 +26973,16 @@
       <c r="I174" s="26"/>
     </row>
     <row r="175" ht="36" customHeight="1" spans="1:11">
-      <c r="A175" s="19"/>
+      <c r="A175" s="19" t="s">
+        <v>233</v>
+      </c>
       <c r="B175" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
+        <v>@HagerHasselhorn2000</v>
       </c>
       <c r="C175" s="21" t="str">
         <f t="shared" si="27"/>
-        <v>[]</v>
+        <v>[@HagerHasselhorn2000]</v>
       </c>
       <c r="D175" s="22" t="str">
         <f t="shared" si="28"/>
@@ -26977,17 +26994,19 @@
       </c>
       <c r="F175" s="23" t="str">
         <f t="shared" si="30"/>
-        <v/>
+        <v>{Evaluation psychologischer Interventionsmaßnahmen}</v>
       </c>
       <c r="G175" s="24" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="H175" s="25" t="str">
+      <c r="H175" s="25">
         <f ca="1" t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="I175" s="26"/>
+        <v>46125.5496643518</v>
+      </c>
+      <c r="I175" s="26" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="176" ht="36" customHeight="1" spans="1:11">
       <c r="A176" s="19"/>
@@ -37342,176 +37361,176 @@
   <sheetData>
     <row r="1" ht="47.25" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="72.75" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" ht="180" customHeight="1" spans="1:3">
       <c r="A5" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" ht="210" customHeight="1" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" ht="210" customHeight="1" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" ht="255" customHeight="1" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" ht="255" customHeight="1" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" ht="285" customHeight="1" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" ht="285" customHeight="1" spans="1:3">
       <c r="A12" s="7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" ht="255" customHeight="1" spans="1:3">
       <c r="A13" s="7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14" ht="165" customHeight="1" spans="1:3">
       <c r="A14" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" ht="165" customHeight="1" spans="1:3">
       <c r="A15" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" ht="165" customHeight="1" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17" ht="225" customHeight="1" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" ht="180" customHeight="1" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" ht="105" customHeight="1" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" ht="120" customHeight="1" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" ht="135" customHeight="1" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/References.xlsx
+++ b/References.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="284">
   <si>
     <t>@article{example2024,   title = {A Reference Example},   journal = {Journal of Examples},   publisher = {Example Press},   author = {Doe, Jane},   year = {2024},   month = aug,   pages = {185–209} }</t>
   </si>
@@ -2796,6 +2796,78 @@
     <t>definition</t>
   </si>
   <si>
+    <t>@book{sedlmeier_forschungsmethoden_2018,
+ author = {Sedlmeier, Peter and Renkewitz, Frank},
+ title = {Forschungsmethoden und Statistik für Psychologen und Sozialwissenschaftler},
+ edition = {3., aktualisierte und erweiterte Auflage},
+ year = {2018},
+ publisher = {Pearson Deutschland GmbH},
+ address = {Hallbergmoos},
+ isbn = {978-3-86894-321-4}
+}</t>
+  </si>
+  <si>
+    <t>@article{PANAS,
+  doi = {10.6102/ZIS242},
+  url = {http://zis.gesis.org/DoiId/zis242},
+  author = {Breyer,  B. and Bluemke,  M.},
+  keywords = {Affektivit\"{a}t,  Wohlbefinden,  Gef\"{u}hl,  Emotion},
+  language = {de},
+  title = {Deutsche Version der Positive and Negative Affect Schedule PANAS (GESIS Panel)},
+  journal = {Zusammenstellung sozialwissenschaftlicher Items und Skalen (ZIS)},
+  publisher = {ZIS - GESIS Leibniz Institute for the Social Sciences},
+  year = {2016},
+  copyright = {Nutzungsbedingungen: Alle in ZIS dokumentierten Erhebungsinstrumente d\"{u}rfen kostenfrei f\"{u}r nicht-kommerzielle Forschungszwecke verwendet werden.Bei einem Einsatz f\"{u}r andere Zwecke oder in einer anderen als der hier dokumentierten Form ist das Einverst\"{a}ndnis der Autoren bzw. Autorinnen einzuholen. In allen resultierenden Arbeiten und Publikationen ist die ZIS-Dokumentation als Quelle anzugeben.}
+}</t>
+  </si>
+  <si>
+    <t>@article{mcauley_long-term_1993,
+ author = {McAuley, Edward and Lox, Curt and Duncan, Terry E.},
+ title = {Long-term maintenance of exercise, self-efficacy, and physiological change in older adults},
+ journal = {Journal of Gerontology: Psychological Sciences},
+ volume = {48},
+ number = {4},
+ pages = {P218-P224},
+ year = {1993},
+ publisher = {The Gerontological Society of America}
+}</t>
+  </si>
+  <si>
+    <t>@misc{grossheinrich_panas-c-p_2020,
+ author = {Großheinrich, N.},
+ title = {PANAS-C-P: Parent Version of the Positive and Negative Affect Scale for Children - deutsche Fassung},
+ year = {2020},
+ publisher = {ZPID (Leibniz-Institut für Psychologie)},
+ series = {Open Test Archive},
+ address = {Trier},
+ doi = {10.23668/psycharchives.4491},
+ url = {https://www.testarchiv.eu/de/test/9007913}
+}</t>
+  </si>
+  <si>
+    <t>@article{resnick_testing_2000,
+ author = {Resnick, B. and Jenkins, L. S.},
+ title = {Testing the reliability and validity of the Self-Efficacy for Exercise Scale},
+ journal = {Nursing Research},
+ volume = {49},
+ number = {3},
+ pages = {154-159},
+ year = {2000}
+}</t>
+  </si>
+  <si>
+    <t>@article{laurent_measure_1999,
+ author = {Laurent, J. and Catanzaro, S. J. and Joiner, T. E. Jr. and Rudolph, K. D. and Potter, K. I. and Lambert, S. and Osborne, L. and Gathright, T.},
+ title = {A measure of positive and negative affect for children: Scale development and preliminary validation},
+ journal = {Psychological Assessment},
+ volume = {11},
+ number = {3},
+ pages = {326-338},
+ year = {1999},
+ doi = {10.1037/1040-3590.11.3.326}
+}</t>
+  </si>
+  <si>
     <t>Bibtex templates</t>
   </si>
   <si>
@@ -27009,196 +27081,214 @@
       </c>
     </row>
     <row r="176" ht="36" customHeight="1" spans="1:11">
-      <c r="A176" s="19"/>
+      <c r="A176" s="19" t="s">
+        <v>235</v>
+      </c>
       <c r="B176" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
+        <v>@sedlmeier_forschungsmethoden_2018</v>
       </c>
       <c r="C176" s="21" t="str">
         <f t="shared" si="27"/>
-        <v>[]</v>
+        <v>[@sedlmeier_forschungsmethoden_2018]</v>
       </c>
       <c r="D176" s="22" t="str">
         <f t="shared" si="28"/>
-        <v/>
+        <v>2018</v>
       </c>
       <c r="E176" s="22" t="str">
         <f t="shared" si="29"/>
-        <v/>
+        <v>Sedlmeier, Peter and Renkewitz, Frank</v>
       </c>
       <c r="F176" s="23" t="str">
         <f t="shared" si="30"/>
-        <v/>
+        <v>Forschungsmethoden und Statistik für Psychologen und Sozialwissenschaftler</v>
       </c>
       <c r="G176" s="24" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="H176" s="25" t="str">
+      <c r="H176" s="25">
         <f ca="1" t="shared" si="32"/>
-        <v/>
+        <v>46129.4323032407</v>
       </c>
       <c r="I176" s="26"/>
     </row>
     <row r="177" ht="36" customHeight="1" spans="1:9">
-      <c r="A177" s="19"/>
+      <c r="A177" s="19" t="s">
+        <v>236</v>
+      </c>
       <c r="B177" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
+        <v>@PANAS</v>
       </c>
       <c r="C177" s="21" t="str">
         <f t="shared" si="27"/>
-        <v>[]</v>
+        <v>[@PANAS]</v>
       </c>
       <c r="D177" s="22" t="str">
         <f t="shared" si="28"/>
-        <v/>
+        <v>2016</v>
       </c>
       <c r="E177" s="22" t="str">
         <f t="shared" si="29"/>
-        <v/>
+        <v>Breyer,  B. and Bluemke,  M.</v>
       </c>
       <c r="F177" s="23" t="str">
         <f t="shared" si="30"/>
-        <v/>
+        <v>Deutsche Version der Positive and Negative Affect Schedule PANAS (GESIS Panel)</v>
       </c>
       <c r="G177" s="24" t="str">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="H177" s="25" t="str">
+        <v>https://doi.org/10.6102/ZIS242</v>
+      </c>
+      <c r="H177" s="25">
         <f ca="1" t="shared" si="32"/>
-        <v/>
+        <v>46129.6597453704</v>
       </c>
       <c r="I177" s="26"/>
     </row>
     <row r="178" ht="36" customHeight="1" spans="1:9">
-      <c r="A178" s="19"/>
+      <c r="A178" s="19" t="s">
+        <v>237</v>
+      </c>
       <c r="B178" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
+        <v>@mcauley_long-term_1993</v>
       </c>
       <c r="C178" s="21" t="str">
         <f t="shared" si="27"/>
-        <v>[]</v>
+        <v>[@mcauley_long-term_1993]</v>
       </c>
       <c r="D178" s="22" t="str">
         <f t="shared" si="28"/>
-        <v/>
+        <v>1993</v>
       </c>
       <c r="E178" s="22" t="str">
         <f t="shared" si="29"/>
-        <v/>
+        <v>McAuley, Edward and Lox, Curt and Duncan, Terry E.</v>
       </c>
       <c r="F178" s="23" t="str">
         <f t="shared" si="30"/>
-        <v/>
+        <v>Long-term maintenance of exercise, self-efficacy, and physiological change in older adults</v>
       </c>
       <c r="G178" s="24" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="H178" s="25" t="str">
+      <c r="H178" s="25">
         <f ca="1" t="shared" si="32"/>
-        <v/>
+        <v>46129.6695833333</v>
       </c>
       <c r="I178" s="26"/>
     </row>
     <row r="179" ht="36" customHeight="1" spans="1:9">
-      <c r="A179" s="19"/>
+      <c r="A179" s="19" t="s">
+        <v>238</v>
+      </c>
       <c r="B179" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
+        <v>@grossheinrich_panas-c-p_2020</v>
       </c>
       <c r="C179" s="21" t="str">
         <f t="shared" si="27"/>
-        <v>[]</v>
+        <v>[@grossheinrich_panas-c-p_2020]</v>
       </c>
       <c r="D179" s="22" t="str">
         <f t="shared" si="28"/>
-        <v/>
+        <v>2020</v>
       </c>
       <c r="E179" s="22" t="str">
         <f t="shared" si="29"/>
-        <v/>
+        <v>Großheinrich, N.</v>
       </c>
       <c r="F179" s="23" t="str">
         <f t="shared" si="30"/>
-        <v/>
+        <v>PANAS-C-P: Parent Version of the Positive and Negative Affect Scale for Children - deutsche Fassung</v>
       </c>
       <c r="G179" s="24" t="str">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="H179" s="25" t="str">
+        <v>https://doi.org/10.23668/psycharchives.4491</v>
+      </c>
+      <c r="H179" s="25">
         <f ca="1" t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="I179" s="26"/>
+        <v>46131.7777199074</v>
+      </c>
+      <c r="I179" s="26" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="180" ht="36" customHeight="1" spans="1:9">
-      <c r="A180" s="19"/>
+      <c r="A180" s="19" t="s">
+        <v>239</v>
+      </c>
       <c r="B180" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
+        <v>@resnick_testing_2000</v>
       </c>
       <c r="C180" s="21" t="str">
         <f t="shared" si="27"/>
-        <v>[]</v>
+        <v>[@resnick_testing_2000]</v>
       </c>
       <c r="D180" s="22" t="str">
         <f t="shared" si="28"/>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="E180" s="22" t="str">
         <f t="shared" si="29"/>
-        <v/>
+        <v>Resnick, B. and Jenkins, L. S.</v>
       </c>
       <c r="F180" s="23" t="str">
         <f t="shared" si="30"/>
-        <v/>
+        <v>Testing the reliability and validity of the Self-Efficacy for Exercise Scale</v>
       </c>
       <c r="G180" s="24" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="H180" s="25" t="str">
+      <c r="H180" s="25">
         <f ca="1" t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="I180" s="26"/>
+        <v>46131.7778472222</v>
+      </c>
+      <c r="I180" s="26" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="181" ht="36" customHeight="1" spans="1:9">
-      <c r="A181" s="19"/>
+      <c r="A181" s="19" t="s">
+        <v>240</v>
+      </c>
       <c r="B181" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
+        <v>@laurent_measure_1999</v>
       </c>
       <c r="C181" s="21" t="str">
         <f t="shared" si="27"/>
-        <v>[]</v>
+        <v>[@laurent_measure_1999]</v>
       </c>
       <c r="D181" s="22" t="str">
         <f t="shared" si="28"/>
-        <v/>
+        <v>1999</v>
       </c>
       <c r="E181" s="22" t="str">
         <f t="shared" si="29"/>
-        <v/>
+        <v>Laurent, J. and Catanzaro, S. J. and Joiner, T. E. Jr. and Rudolph, K. D. and Potter, K. I. and Lambert, S. and Osborne, L. and Gathright, T.</v>
       </c>
       <c r="F181" s="23" t="str">
         <f t="shared" si="30"/>
-        <v/>
+        <v>A measure of positive and negative affect for children: Scale development and preliminary validation</v>
       </c>
       <c r="G181" s="24" t="str">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="H181" s="25" t="str">
+        <v>https://doi.org/10.1037/1040-3590.11.3.326</v>
+      </c>
+      <c r="H181" s="25">
         <f ca="1" t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="I181" s="26"/>
+        <v>46131.7779398148</v>
+      </c>
+      <c r="I181" s="26" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="182" ht="36" customHeight="1" spans="1:9">
       <c r="A182" s="19"/>
@@ -37361,176 +37451,176 @@
   <sheetData>
     <row r="1" ht="47.25" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="72.75" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" ht="180" customHeight="1" spans="1:3">
       <c r="A5" s="7" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" ht="210" customHeight="1" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" ht="210" customHeight="1" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" ht="255" customHeight="1" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" ht="255" customHeight="1" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" ht="285" customHeight="1" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" ht="285" customHeight="1" spans="1:3">
       <c r="A12" s="7" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" ht="255" customHeight="1" spans="1:3">
       <c r="A13" s="7" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" ht="165" customHeight="1" spans="1:3">
       <c r="A14" s="7" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" ht="165" customHeight="1" spans="1:3">
       <c r="A15" s="7" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" ht="165" customHeight="1" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17" ht="225" customHeight="1" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" ht="180" customHeight="1" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" ht="105" customHeight="1" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" ht="120" customHeight="1" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" ht="135" customHeight="1" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>

--- a/References.xlsx
+++ b/References.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="287">
   <si>
     <t>@article{example2024,   title = {A Reference Example},   journal = {Journal of Examples},   publisher = {Example Press},   author = {Doe, Jane},   year = {2024},   month = aug,   pages = {185–209} }</t>
   </si>
@@ -2868,6 +2868,53 @@
 }</t>
   </si>
   <si>
+    <t>@article{Wisniewski2019,
+  title = {Understanding the quality,  effectiveness and attributes of top-rated smartphone health apps},
+  volume = {22},
+  ISSN = {1468-960X},
+  url = {http://dx.doi.org/10.1136/ebmental-2018-300069},
+  DOI = {10.1136/ebmental-2018-300069},
+  number = {1},
+  journal = {Evidence Based Mental Health},
+  publisher = {BMJ},
+  author = {Wisniewski,  Hannah and Liu,  Gang and Henson,  Philip and Vaidyam,  Aditya and Hajratalli,  Narissa Karima and Onnela,  Jukka-Pekka and Torous,  John},
+  year = {2019},
+  month = jan,
+  pages = {4–9}
+}</t>
+  </si>
+  <si>
+    <t>@article{Lee2018,
+  title = {Mobile App-Based Health Promotion Programs: A Systematic Review of the Literature},
+  volume = {15},
+  ISSN = {1660-4601},
+  url = {http://dx.doi.org/10.3390/ijerph15122838},
+  DOI = {10.3390/ijerph15122838},
+  number = {12},
+  journal = {International Journal of Environmental Research and Public Health},
+  publisher = {MDPI AG},
+  author = {Lee,  Mikyung and Lee,  Hyeonkyeong and Kim,  Youlim and Kim,  Junghee and Cho,  Mikyeong and Jang,  Jaeun and Jang,  Hyoeun},
+  year = {2018},
+  month = dec,
+  pages = {2838}
+}</t>
+  </si>
+  <si>
+    <t>@article{Tracy_tale_2007,
+  title = {The psychological structure of pride: A tale of two facets.},
+  volume = {92},
+  ISSN = {0022-3514},
+  url = {http://dx.doi.org/10.1037/0022-3514.92.3.506},
+  DOI = {10.1037/0022-3514.92.3.506},
+  number = {3},
+  journal = {Journal of Personality and Social Psychology},
+  publisher = {American Psychological Association (APA)},
+  author = {Tracy,  Jessica L. and Robins,  Richard W.},
+  year = {2007},
+  pages = {506–525}
+}</t>
+  </si>
+  <si>
     <t>Bibtex templates</t>
   </si>
   <si>
@@ -26104,7 +26151,7 @@
         <v>196</v>
       </c>
       <c r="B149" s="20" t="str">
-        <f t="shared" ref="B147:B183" si="26">IFERROR("@"&amp;MID(A149,SEARCH("{",A149)+1,SEARCH(",",A149)-SEARCH("{",A149)-1),"")</f>
+        <f t="shared" ref="B147:B184" si="26">IFERROR("@"&amp;MID(A149,SEARCH("{",A149)+1,SEARCH(",",A149)-SEARCH("{",A149)-1),"")</f>
         <v>@Svendsen2022</v>
       </c>
       <c r="C149" s="21" t="str">
@@ -27291,105 +27338,111 @@
       </c>
     </row>
     <row r="182" ht="36" customHeight="1" spans="1:9">
-      <c r="A182" s="19"/>
+      <c r="A182" s="19" t="s">
+        <v>241</v>
+      </c>
       <c r="B182" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
+        <v>@Wisniewski2019</v>
       </c>
       <c r="C182" s="21" t="str">
         <f t="shared" si="27"/>
-        <v>[]</v>
+        <v>[@Wisniewski2019]</v>
       </c>
       <c r="D182" s="22" t="str">
         <f t="shared" si="28"/>
-        <v/>
+        <v>2019</v>
       </c>
       <c r="E182" s="22" t="str">
         <f t="shared" si="29"/>
-        <v/>
+        <v>Wisniewski,  Hannah and Liu,  Gang and Henson,  Philip and Vaidyam,  Aditya and Hajratalli,  Narissa Karima and Onnela,  Jukka-Pekka and Torous,  John</v>
       </c>
       <c r="F182" s="23" t="str">
         <f t="shared" si="30"/>
-        <v/>
+        <v>Understanding the quality,  effectiveness and attributes of top-rated smartphone health apps</v>
       </c>
       <c r="G182" s="24" t="str">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="H182" s="25" t="str">
+        <v>https://doi.org/10.1136/ebmental-2018-300069</v>
+      </c>
+      <c r="H182" s="25">
         <f ca="1" t="shared" si="32"/>
-        <v/>
+        <v>46132.6110416667</v>
       </c>
       <c r="I182" s="26"/>
     </row>
     <row r="183" ht="36" customHeight="1" spans="1:9">
-      <c r="A183" s="19"/>
+      <c r="A183" s="19" t="s">
+        <v>242</v>
+      </c>
       <c r="B183" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
+        <v>@Lee2018</v>
       </c>
       <c r="C183" s="21" t="str">
         <f t="shared" si="27"/>
-        <v>[]</v>
+        <v>[@Lee2018]</v>
       </c>
       <c r="D183" s="22" t="str">
         <f t="shared" si="28"/>
-        <v/>
+        <v>2018</v>
       </c>
       <c r="E183" s="22" t="str">
         <f t="shared" si="29"/>
-        <v/>
+        <v>Lee,  Mikyung and Lee,  Hyeonkyeong and Kim,  Youlim and Kim,  Junghee and Cho,  Mikyeong and Jang,  Jaeun and Jang,  Hyoeun</v>
       </c>
       <c r="F183" s="23" t="str">
         <f t="shared" si="30"/>
-        <v/>
+        <v>Mobile App-Based Health Promotion Programs: A Systematic Review of the Literature</v>
       </c>
       <c r="G183" s="24" t="str">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="H183" s="25" t="str">
+        <v>https://doi.org/10.3390/ijerph15122838</v>
+      </c>
+      <c r="H183" s="25">
         <f ca="1" t="shared" si="32"/>
-        <v/>
+        <v>46132.6115509259</v>
       </c>
       <c r="I183" s="26"/>
     </row>
     <row r="184" ht="36" customHeight="1" spans="1:9">
-      <c r="A184" s="19"/>
+      <c r="A184" s="19" t="s">
+        <v>243</v>
+      </c>
       <c r="B184" s="20" t="str">
-        <f t="shared" ref="B184:B247" si="33">IFERROR("@"&amp;MID(A184,SEARCH("{",A184)+1,SEARCH(",",A184)-SEARCH("{",A184)-1),"")</f>
-        <v/>
+        <f t="shared" si="26"/>
+        <v>@Tracy_tale_2007</v>
       </c>
       <c r="C184" s="21" t="str">
         <f t="shared" si="27"/>
-        <v>[]</v>
+        <v>[@Tracy_tale_2007]</v>
       </c>
       <c r="D184" s="22" t="str">
-        <f t="shared" ref="D184:D247" si="34">IFERROR(MID(A184,SEARCH("year = {",A184)+8,4),"")</f>
-        <v/>
+        <f t="shared" ref="D184:D247" si="33">IFERROR(MID(A184,SEARCH("year = {",A184)+8,4),"")</f>
+        <v>2007</v>
       </c>
       <c r="E184" s="22" t="str">
-        <f t="shared" ref="E184:E247" si="35">IFERROR(MID(A184,SEARCH("author = {",A184)+10,SEARCH("}",A184,SEARCH("author = {",A184))-SEARCH("author = {",A184)-10),"")</f>
-        <v/>
+        <f t="shared" ref="E184:E247" si="34">IFERROR(MID(A184,SEARCH("author = {",A184)+10,SEARCH("}",A184,SEARCH("author = {",A184))-SEARCH("author = {",A184)-10),"")</f>
+        <v>Tracy,  Jessica L. and Robins,  Richard W.</v>
       </c>
       <c r="F184" s="23" t="str">
-        <f t="shared" ref="F184:F247" si="36">IFERROR(IF(ISERROR(FIND("title =",A184)),"",MID(A184,FIND("title =",A184)+9,FIND("},",A184,FIND("title =",A184))-FIND("title =",A184)-9)),"")</f>
-        <v/>
+        <f t="shared" ref="F184:F247" si="35">IFERROR(IF(ISERROR(FIND("title =",A184)),"",MID(A184,FIND("title =",A184)+9,FIND("},",A184,FIND("title =",A184))-FIND("title =",A184)-9)),"")</f>
+        <v>The psychological structure of pride: A tale of two facets.</v>
       </c>
       <c r="G184" s="24" t="str">
-        <f t="shared" ref="G184:G247" si="37">IFERROR("https://doi.org/"&amp;MID(A184,SEARCH("doi = {",A184)+7,FIND("}",A184,SEARCH("doi = {",A184))-SEARCH("doi = {",A184)-7),"")</f>
-        <v/>
-      </c>
-      <c r="H184" s="25" t="str">
-        <f ca="1" t="shared" ref="H184:H247" si="38">IF(A184&lt;&gt;"",IF(H184&lt;&gt;"",H184,NOW()),"")</f>
-        <v/>
+        <f t="shared" ref="G184:G247" si="36">IFERROR("https://doi.org/"&amp;MID(A184,SEARCH("doi = {",A184)+7,FIND("}",A184,SEARCH("doi = {",A184))-SEARCH("doi = {",A184)-7),"")</f>
+        <v>https://doi.org/10.1037/0022-3514.92.3.506</v>
+      </c>
+      <c r="H184" s="25">
+        <f ca="1" t="shared" ref="H184:H247" si="37">IF(A184&lt;&gt;"",IF(H184&lt;&gt;"",H184,NOW()),"")</f>
+        <v>46132.7114467593</v>
       </c>
       <c r="I184" s="26"/>
     </row>
     <row r="185" ht="36" customHeight="1" spans="1:9">
       <c r="A185" s="19"/>
       <c r="B185" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="B184:B247" si="38">IFERROR("@"&amp;MID(A185,SEARCH("{",A185)+1,SEARCH(",",A185)-SEARCH("{",A185)-1),"")</f>
         <v/>
       </c>
       <c r="C185" s="21" t="str">
@@ -27397,23 +27450,23 @@
         <v>[]</v>
       </c>
       <c r="D185" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E185" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E185" s="22" t="str">
+      <c r="F185" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F185" s="23" t="str">
+      <c r="G185" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G185" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H185" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I185" s="26"/>
@@ -27421,7 +27474,7 @@
     <row r="186" ht="36" customHeight="1" spans="1:9">
       <c r="A186" s="19"/>
       <c r="B186" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C186" s="21" t="str">
@@ -27429,23 +27482,23 @@
         <v>[]</v>
       </c>
       <c r="D186" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E186" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E186" s="22" t="str">
+      <c r="F186" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F186" s="23" t="str">
+      <c r="G186" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G186" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H186" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I186" s="26"/>
@@ -27453,7 +27506,7 @@
     <row r="187" ht="36" customHeight="1" spans="1:9">
       <c r="A187" s="19"/>
       <c r="B187" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C187" s="21" t="str">
@@ -27461,23 +27514,23 @@
         <v>[]</v>
       </c>
       <c r="D187" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E187" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E187" s="22" t="str">
+      <c r="F187" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F187" s="23" t="str">
+      <c r="G187" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G187" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H187" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I187" s="26"/>
@@ -27485,7 +27538,7 @@
     <row r="188" ht="36" customHeight="1" spans="1:9">
       <c r="A188" s="19"/>
       <c r="B188" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C188" s="21" t="str">
@@ -27493,23 +27546,23 @@
         <v>[]</v>
       </c>
       <c r="D188" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E188" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E188" s="22" t="str">
+      <c r="F188" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F188" s="23" t="str">
+      <c r="G188" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G188" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H188" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I188" s="26"/>
@@ -27517,7 +27570,7 @@
     <row r="189" ht="36" customHeight="1" spans="1:9">
       <c r="A189" s="19"/>
       <c r="B189" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C189" s="21" t="str">
@@ -27525,23 +27578,23 @@
         <v>[]</v>
       </c>
       <c r="D189" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E189" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E189" s="22" t="str">
+      <c r="F189" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F189" s="23" t="str">
+      <c r="G189" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G189" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H189" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I189" s="26"/>
@@ -27549,7 +27602,7 @@
     <row r="190" ht="36" customHeight="1" spans="1:9">
       <c r="A190" s="19"/>
       <c r="B190" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C190" s="21" t="str">
@@ -27557,23 +27610,23 @@
         <v>[]</v>
       </c>
       <c r="D190" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E190" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E190" s="22" t="str">
+      <c r="F190" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F190" s="23" t="str">
+      <c r="G190" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G190" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H190" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I190" s="26"/>
@@ -27581,7 +27634,7 @@
     <row r="191" ht="36" customHeight="1" spans="1:9">
       <c r="A191" s="19"/>
       <c r="B191" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C191" s="21" t="str">
@@ -27589,23 +27642,23 @@
         <v>[]</v>
       </c>
       <c r="D191" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E191" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E191" s="22" t="str">
+      <c r="F191" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F191" s="23" t="str">
+      <c r="G191" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G191" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H191" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I191" s="26"/>
@@ -27613,7 +27666,7 @@
     <row r="192" ht="36" customHeight="1" spans="1:9">
       <c r="A192" s="19"/>
       <c r="B192" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C192" s="21" t="str">
@@ -27621,23 +27674,23 @@
         <v>[]</v>
       </c>
       <c r="D192" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E192" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E192" s="22" t="str">
+      <c r="F192" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F192" s="23" t="str">
+      <c r="G192" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G192" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H192" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I192" s="26"/>
@@ -27645,7 +27698,7 @@
     <row r="193" ht="36" customHeight="1" spans="1:9">
       <c r="A193" s="19"/>
       <c r="B193" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C193" s="21" t="str">
@@ -27653,23 +27706,23 @@
         <v>[]</v>
       </c>
       <c r="D193" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E193" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E193" s="22" t="str">
+      <c r="F193" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F193" s="23" t="str">
+      <c r="G193" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G193" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H193" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I193" s="26"/>
@@ -27677,7 +27730,7 @@
     <row r="194" ht="36" customHeight="1" spans="1:9">
       <c r="A194" s="19"/>
       <c r="B194" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C194" s="21" t="str">
@@ -27685,23 +27738,23 @@
         <v>[]</v>
       </c>
       <c r="D194" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E194" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E194" s="22" t="str">
+      <c r="F194" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F194" s="23" t="str">
+      <c r="G194" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G194" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H194" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I194" s="26"/>
@@ -27709,7 +27762,7 @@
     <row r="195" ht="36" customHeight="1" spans="1:9">
       <c r="A195" s="19"/>
       <c r="B195" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C195" s="21" t="str">
@@ -27717,23 +27770,23 @@
         <v>[]</v>
       </c>
       <c r="D195" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E195" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E195" s="22" t="str">
+      <c r="F195" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F195" s="23" t="str">
+      <c r="G195" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G195" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H195" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I195" s="26"/>
@@ -27741,7 +27794,7 @@
     <row r="196" ht="36" customHeight="1" spans="1:9">
       <c r="A196" s="19"/>
       <c r="B196" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C196" s="21" t="str">
@@ -27749,23 +27802,23 @@
         <v>[]</v>
       </c>
       <c r="D196" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E196" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E196" s="22" t="str">
+      <c r="F196" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F196" s="23" t="str">
+      <c r="G196" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G196" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H196" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I196" s="26"/>
@@ -27773,7 +27826,7 @@
     <row r="197" ht="36" customHeight="1" spans="1:9">
       <c r="A197" s="19"/>
       <c r="B197" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C197" s="21" t="str">
@@ -27781,23 +27834,23 @@
         <v>[]</v>
       </c>
       <c r="D197" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E197" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E197" s="22" t="str">
+      <c r="F197" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F197" s="23" t="str">
+      <c r="G197" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G197" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H197" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I197" s="26"/>
@@ -27805,7 +27858,7 @@
     <row r="198" ht="36" customHeight="1" spans="1:9">
       <c r="A198" s="19"/>
       <c r="B198" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C198" s="21" t="str">
@@ -27813,23 +27866,23 @@
         <v>[]</v>
       </c>
       <c r="D198" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E198" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E198" s="22" t="str">
+      <c r="F198" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F198" s="23" t="str">
+      <c r="G198" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G198" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H198" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I198" s="26"/>
@@ -27837,7 +27890,7 @@
     <row r="199" ht="36" customHeight="1" spans="1:9">
       <c r="A199" s="19"/>
       <c r="B199" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C199" s="21" t="str">
@@ -27845,23 +27898,23 @@
         <v>[]</v>
       </c>
       <c r="D199" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E199" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E199" s="22" t="str">
+      <c r="F199" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F199" s="23" t="str">
+      <c r="G199" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G199" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H199" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I199" s="26"/>
@@ -27869,7 +27922,7 @@
     <row r="200" ht="36" customHeight="1" spans="1:9">
       <c r="A200" s="19"/>
       <c r="B200" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C200" s="21" t="str">
@@ -27877,23 +27930,23 @@
         <v>[]</v>
       </c>
       <c r="D200" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E200" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E200" s="22" t="str">
+      <c r="F200" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F200" s="23" t="str">
+      <c r="G200" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G200" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H200" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I200" s="26"/>
@@ -27901,7 +27954,7 @@
     <row r="201" ht="36" customHeight="1" spans="1:9">
       <c r="A201" s="19"/>
       <c r="B201" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C201" s="21" t="str">
@@ -27909,23 +27962,23 @@
         <v>[]</v>
       </c>
       <c r="D201" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E201" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E201" s="22" t="str">
+      <c r="F201" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F201" s="23" t="str">
+      <c r="G201" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G201" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H201" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I201" s="26"/>
@@ -27933,7 +27986,7 @@
     <row r="202" ht="36" customHeight="1" spans="1:9">
       <c r="A202" s="19"/>
       <c r="B202" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C202" s="21" t="str">
@@ -27941,23 +27994,23 @@
         <v>[]</v>
       </c>
       <c r="D202" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E202" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E202" s="22" t="str">
+      <c r="F202" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F202" s="23" t="str">
+      <c r="G202" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G202" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H202" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I202" s="26"/>
@@ -27965,7 +28018,7 @@
     <row r="203" ht="36" customHeight="1" spans="1:9">
       <c r="A203" s="19"/>
       <c r="B203" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C203" s="21" t="str">
@@ -27973,23 +28026,23 @@
         <v>[]</v>
       </c>
       <c r="D203" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E203" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E203" s="22" t="str">
+      <c r="F203" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F203" s="23" t="str">
+      <c r="G203" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G203" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H203" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I203" s="26"/>
@@ -27997,7 +28050,7 @@
     <row r="204" ht="36" customHeight="1" spans="1:9">
       <c r="A204" s="19"/>
       <c r="B204" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C204" s="21" t="str">
@@ -28005,23 +28058,23 @@
         <v>[]</v>
       </c>
       <c r="D204" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E204" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E204" s="22" t="str">
+      <c r="F204" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F204" s="23" t="str">
+      <c r="G204" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G204" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H204" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I204" s="26"/>
@@ -28029,7 +28082,7 @@
     <row r="205" ht="36" customHeight="1" spans="1:9">
       <c r="A205" s="19"/>
       <c r="B205" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C205" s="21" t="str">
@@ -28037,23 +28090,23 @@
         <v>[]</v>
       </c>
       <c r="D205" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E205" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E205" s="22" t="str">
+      <c r="F205" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F205" s="23" t="str">
+      <c r="G205" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G205" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H205" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I205" s="26"/>
@@ -28061,7 +28114,7 @@
     <row r="206" ht="36" customHeight="1" spans="1:9">
       <c r="A206" s="19"/>
       <c r="B206" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C206" s="21" t="str">
@@ -28069,23 +28122,23 @@
         <v>[]</v>
       </c>
       <c r="D206" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E206" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E206" s="22" t="str">
+      <c r="F206" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F206" s="23" t="str">
+      <c r="G206" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G206" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H206" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I206" s="26"/>
@@ -28093,7 +28146,7 @@
     <row r="207" ht="36" customHeight="1" spans="1:9">
       <c r="A207" s="19"/>
       <c r="B207" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C207" s="21" t="str">
@@ -28101,23 +28154,23 @@
         <v>[]</v>
       </c>
       <c r="D207" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E207" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E207" s="22" t="str">
+      <c r="F207" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F207" s="23" t="str">
+      <c r="G207" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G207" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H207" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I207" s="26"/>
@@ -28125,7 +28178,7 @@
     <row r="208" ht="36" customHeight="1" spans="1:9">
       <c r="A208" s="19"/>
       <c r="B208" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C208" s="21" t="str">
@@ -28133,23 +28186,23 @@
         <v>[]</v>
       </c>
       <c r="D208" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E208" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E208" s="22" t="str">
+      <c r="F208" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F208" s="23" t="str">
+      <c r="G208" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G208" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H208" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I208" s="26"/>
@@ -28157,7 +28210,7 @@
     <row r="209" ht="36" customHeight="1" spans="1:9">
       <c r="A209" s="19"/>
       <c r="B209" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C209" s="21" t="str">
@@ -28165,23 +28218,23 @@
         <v>[]</v>
       </c>
       <c r="D209" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E209" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E209" s="22" t="str">
+      <c r="F209" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F209" s="23" t="str">
+      <c r="G209" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G209" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H209" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I209" s="26"/>
@@ -28189,7 +28242,7 @@
     <row r="210" ht="36" customHeight="1" spans="1:9">
       <c r="A210" s="19"/>
       <c r="B210" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C210" s="21" t="str">
@@ -28197,23 +28250,23 @@
         <v>[]</v>
       </c>
       <c r="D210" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E210" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E210" s="22" t="str">
+      <c r="F210" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F210" s="23" t="str">
+      <c r="G210" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G210" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H210" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I210" s="26"/>
@@ -28221,7 +28274,7 @@
     <row r="211" ht="36" customHeight="1" spans="1:9">
       <c r="A211" s="19"/>
       <c r="B211" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C211" s="21" t="str">
@@ -28229,23 +28282,23 @@
         <v>[]</v>
       </c>
       <c r="D211" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E211" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E211" s="22" t="str">
+      <c r="F211" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F211" s="23" t="str">
+      <c r="G211" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G211" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H211" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I211" s="26"/>
@@ -28253,7 +28306,7 @@
     <row r="212" ht="36" customHeight="1" spans="1:9">
       <c r="A212" s="19"/>
       <c r="B212" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C212" s="21" t="str">
@@ -28261,23 +28314,23 @@
         <v>[]</v>
       </c>
       <c r="D212" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E212" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E212" s="22" t="str">
+      <c r="F212" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F212" s="23" t="str">
+      <c r="G212" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G212" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H212" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I212" s="26"/>
@@ -28285,7 +28338,7 @@
     <row r="213" ht="36" customHeight="1" spans="1:9">
       <c r="A213" s="19"/>
       <c r="B213" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C213" s="21" t="str">
@@ -28293,23 +28346,23 @@
         <v>[]</v>
       </c>
       <c r="D213" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E213" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E213" s="22" t="str">
+      <c r="F213" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F213" s="23" t="str">
+      <c r="G213" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G213" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H213" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I213" s="26"/>
@@ -28317,7 +28370,7 @@
     <row r="214" ht="36" customHeight="1" spans="1:9">
       <c r="A214" s="19"/>
       <c r="B214" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C214" s="21" t="str">
@@ -28325,23 +28378,23 @@
         <v>[]</v>
       </c>
       <c r="D214" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E214" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E214" s="22" t="str">
+      <c r="F214" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F214" s="23" t="str">
+      <c r="G214" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G214" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H214" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I214" s="26"/>
@@ -28349,7 +28402,7 @@
     <row r="215" ht="36" customHeight="1" spans="1:9">
       <c r="A215" s="19"/>
       <c r="B215" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C215" s="21" t="str">
@@ -28357,23 +28410,23 @@
         <v>[]</v>
       </c>
       <c r="D215" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E215" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E215" s="22" t="str">
+      <c r="F215" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F215" s="23" t="str">
+      <c r="G215" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G215" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H215" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I215" s="26"/>
@@ -28381,7 +28434,7 @@
     <row r="216" ht="36" customHeight="1" spans="1:9">
       <c r="A216" s="19"/>
       <c r="B216" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C216" s="21" t="str">
@@ -28389,23 +28442,23 @@
         <v>[]</v>
       </c>
       <c r="D216" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E216" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E216" s="22" t="str">
+      <c r="F216" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F216" s="23" t="str">
+      <c r="G216" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G216" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H216" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I216" s="26"/>
@@ -28413,7 +28466,7 @@
     <row r="217" ht="36" customHeight="1" spans="1:9">
       <c r="A217" s="19"/>
       <c r="B217" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C217" s="21" t="str">
@@ -28421,23 +28474,23 @@
         <v>[]</v>
       </c>
       <c r="D217" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E217" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E217" s="22" t="str">
+      <c r="F217" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F217" s="23" t="str">
+      <c r="G217" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G217" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H217" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I217" s="26"/>
@@ -28445,7 +28498,7 @@
     <row r="218" ht="36" customHeight="1" spans="1:9">
       <c r="A218" s="19"/>
       <c r="B218" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C218" s="21" t="str">
@@ -28453,23 +28506,23 @@
         <v>[]</v>
       </c>
       <c r="D218" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E218" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E218" s="22" t="str">
+      <c r="F218" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F218" s="23" t="str">
+      <c r="G218" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G218" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H218" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I218" s="26"/>
@@ -28477,7 +28530,7 @@
     <row r="219" ht="36" customHeight="1" spans="1:9">
       <c r="A219" s="19"/>
       <c r="B219" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C219" s="21" t="str">
@@ -28485,23 +28538,23 @@
         <v>[]</v>
       </c>
       <c r="D219" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E219" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E219" s="22" t="str">
+      <c r="F219" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F219" s="23" t="str">
+      <c r="G219" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G219" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H219" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I219" s="26"/>
@@ -28509,7 +28562,7 @@
     <row r="220" ht="36" customHeight="1" spans="1:9">
       <c r="A220" s="19"/>
       <c r="B220" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C220" s="21" t="str">
@@ -28517,23 +28570,23 @@
         <v>[]</v>
       </c>
       <c r="D220" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E220" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E220" s="22" t="str">
+      <c r="F220" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F220" s="23" t="str">
+      <c r="G220" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G220" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H220" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I220" s="26"/>
@@ -28541,7 +28594,7 @@
     <row r="221" ht="36" customHeight="1" spans="1:9">
       <c r="A221" s="19"/>
       <c r="B221" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C221" s="21" t="str">
@@ -28549,23 +28602,23 @@
         <v>[]</v>
       </c>
       <c r="D221" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E221" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E221" s="22" t="str">
+      <c r="F221" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F221" s="23" t="str">
+      <c r="G221" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G221" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H221" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I221" s="26"/>
@@ -28573,7 +28626,7 @@
     <row r="222" ht="36" customHeight="1" spans="1:9">
       <c r="A222" s="19"/>
       <c r="B222" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C222" s="21" t="str">
@@ -28581,23 +28634,23 @@
         <v>[]</v>
       </c>
       <c r="D222" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E222" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E222" s="22" t="str">
+      <c r="F222" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F222" s="23" t="str">
+      <c r="G222" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G222" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H222" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I222" s="26"/>
@@ -28605,7 +28658,7 @@
     <row r="223" ht="36" customHeight="1" spans="1:9">
       <c r="A223" s="19"/>
       <c r="B223" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C223" s="21" t="str">
@@ -28613,23 +28666,23 @@
         <v>[]</v>
       </c>
       <c r="D223" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E223" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E223" s="22" t="str">
+      <c r="F223" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F223" s="23" t="str">
+      <c r="G223" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G223" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H223" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I223" s="26"/>
@@ -28637,7 +28690,7 @@
     <row r="224" ht="36" customHeight="1" spans="1:9">
       <c r="A224" s="19"/>
       <c r="B224" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C224" s="21" t="str">
@@ -28645,23 +28698,23 @@
         <v>[]</v>
       </c>
       <c r="D224" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E224" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E224" s="22" t="str">
+      <c r="F224" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F224" s="23" t="str">
+      <c r="G224" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G224" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H224" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I224" s="26"/>
@@ -28669,7 +28722,7 @@
     <row r="225" ht="36" customHeight="1" spans="1:9">
       <c r="A225" s="19"/>
       <c r="B225" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C225" s="21" t="str">
@@ -28677,23 +28730,23 @@
         <v>[]</v>
       </c>
       <c r="D225" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E225" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E225" s="22" t="str">
+      <c r="F225" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F225" s="23" t="str">
+      <c r="G225" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G225" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H225" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I225" s="26"/>
@@ -28701,7 +28754,7 @@
     <row r="226" ht="36" customHeight="1" spans="1:9">
       <c r="A226" s="19"/>
       <c r="B226" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C226" s="21" t="str">
@@ -28709,23 +28762,23 @@
         <v>[]</v>
       </c>
       <c r="D226" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E226" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E226" s="22" t="str">
+      <c r="F226" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F226" s="23" t="str">
+      <c r="G226" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G226" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H226" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I226" s="26"/>
@@ -28733,7 +28786,7 @@
     <row r="227" ht="36" customHeight="1" spans="1:9">
       <c r="A227" s="19"/>
       <c r="B227" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C227" s="21" t="str">
@@ -28741,23 +28794,23 @@
         <v>[]</v>
       </c>
       <c r="D227" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E227" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E227" s="22" t="str">
+      <c r="F227" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F227" s="23" t="str">
+      <c r="G227" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G227" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H227" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I227" s="26"/>
@@ -28765,7 +28818,7 @@
     <row r="228" ht="36" customHeight="1" spans="1:9">
       <c r="A228" s="19"/>
       <c r="B228" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C228" s="21" t="str">
@@ -28773,23 +28826,23 @@
         <v>[]</v>
       </c>
       <c r="D228" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E228" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E228" s="22" t="str">
+      <c r="F228" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F228" s="23" t="str">
+      <c r="G228" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G228" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H228" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I228" s="26"/>
@@ -28797,7 +28850,7 @@
     <row r="229" ht="36" customHeight="1" spans="1:9">
       <c r="A229" s="19"/>
       <c r="B229" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C229" s="21" t="str">
@@ -28805,23 +28858,23 @@
         <v>[]</v>
       </c>
       <c r="D229" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E229" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E229" s="22" t="str">
+      <c r="F229" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F229" s="23" t="str">
+      <c r="G229" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G229" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H229" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I229" s="26"/>
@@ -28829,7 +28882,7 @@
     <row r="230" ht="36" customHeight="1" spans="1:9">
       <c r="A230" s="19"/>
       <c r="B230" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C230" s="21" t="str">
@@ -28837,23 +28890,23 @@
         <v>[]</v>
       </c>
       <c r="D230" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E230" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E230" s="22" t="str">
+      <c r="F230" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F230" s="23" t="str">
+      <c r="G230" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G230" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H230" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I230" s="26"/>
@@ -28861,7 +28914,7 @@
     <row r="231" ht="36" customHeight="1" spans="1:9">
       <c r="A231" s="19"/>
       <c r="B231" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C231" s="21" t="str">
@@ -28869,23 +28922,23 @@
         <v>[]</v>
       </c>
       <c r="D231" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E231" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E231" s="22" t="str">
+      <c r="F231" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F231" s="23" t="str">
+      <c r="G231" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G231" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H231" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I231" s="26"/>
@@ -28893,7 +28946,7 @@
     <row r="232" ht="36" customHeight="1" spans="1:9">
       <c r="A232" s="19"/>
       <c r="B232" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C232" s="21" t="str">
@@ -28901,23 +28954,23 @@
         <v>[]</v>
       </c>
       <c r="D232" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E232" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E232" s="22" t="str">
+      <c r="F232" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F232" s="23" t="str">
+      <c r="G232" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G232" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H232" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I232" s="26"/>
@@ -28925,7 +28978,7 @@
     <row r="233" ht="36" customHeight="1" spans="1:9">
       <c r="A233" s="19"/>
       <c r="B233" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C233" s="21" t="str">
@@ -28933,23 +28986,23 @@
         <v>[]</v>
       </c>
       <c r="D233" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E233" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E233" s="22" t="str">
+      <c r="F233" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F233" s="23" t="str">
+      <c r="G233" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G233" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H233" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I233" s="26"/>
@@ -28957,7 +29010,7 @@
     <row r="234" ht="36" customHeight="1" spans="1:9">
       <c r="A234" s="19"/>
       <c r="B234" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C234" s="21" t="str">
@@ -28965,23 +29018,23 @@
         <v>[]</v>
       </c>
       <c r="D234" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E234" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E234" s="22" t="str">
+      <c r="F234" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F234" s="23" t="str">
+      <c r="G234" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G234" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H234" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I234" s="26"/>
@@ -28989,7 +29042,7 @@
     <row r="235" ht="36" customHeight="1" spans="1:9">
       <c r="A235" s="19"/>
       <c r="B235" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C235" s="21" t="str">
@@ -28997,23 +29050,23 @@
         <v>[]</v>
       </c>
       <c r="D235" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E235" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E235" s="22" t="str">
+      <c r="F235" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F235" s="23" t="str">
+      <c r="G235" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G235" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H235" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I235" s="26"/>
@@ -29021,7 +29074,7 @@
     <row r="236" ht="36" customHeight="1" spans="1:9">
       <c r="A236" s="19"/>
       <c r="B236" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C236" s="21" t="str">
@@ -29029,23 +29082,23 @@
         <v>[]</v>
       </c>
       <c r="D236" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E236" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E236" s="22" t="str">
+      <c r="F236" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F236" s="23" t="str">
+      <c r="G236" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G236" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H236" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I236" s="26"/>
@@ -29053,7 +29106,7 @@
     <row r="237" ht="36" customHeight="1" spans="1:9">
       <c r="A237" s="19"/>
       <c r="B237" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C237" s="21" t="str">
@@ -29061,23 +29114,23 @@
         <v>[]</v>
       </c>
       <c r="D237" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E237" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E237" s="22" t="str">
+      <c r="F237" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F237" s="23" t="str">
+      <c r="G237" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G237" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H237" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I237" s="26"/>
@@ -29085,7 +29138,7 @@
     <row r="238" ht="36" customHeight="1" spans="1:9">
       <c r="A238" s="19"/>
       <c r="B238" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C238" s="21" t="str">
@@ -29093,23 +29146,23 @@
         <v>[]</v>
       </c>
       <c r="D238" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E238" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E238" s="22" t="str">
+      <c r="F238" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F238" s="23" t="str">
+      <c r="G238" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G238" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H238" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I238" s="26"/>
@@ -29117,7 +29170,7 @@
     <row r="239" ht="36" customHeight="1" spans="1:9">
       <c r="A239" s="19"/>
       <c r="B239" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C239" s="21" t="str">
@@ -29125,23 +29178,23 @@
         <v>[]</v>
       </c>
       <c r="D239" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E239" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E239" s="22" t="str">
+      <c r="F239" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F239" s="23" t="str">
+      <c r="G239" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G239" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H239" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I239" s="26"/>
@@ -29149,7 +29202,7 @@
     <row r="240" ht="36" customHeight="1" spans="1:9">
       <c r="A240" s="19"/>
       <c r="B240" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C240" s="21" t="str">
@@ -29157,23 +29210,23 @@
         <v>[]</v>
       </c>
       <c r="D240" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E240" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E240" s="22" t="str">
+      <c r="F240" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F240" s="23" t="str">
+      <c r="G240" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G240" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H240" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I240" s="26"/>
@@ -29181,7 +29234,7 @@
     <row r="241" ht="36" customHeight="1" spans="1:9">
       <c r="A241" s="19"/>
       <c r="B241" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C241" s="21" t="str">
@@ -29189,23 +29242,23 @@
         <v>[]</v>
       </c>
       <c r="D241" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E241" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E241" s="22" t="str">
+      <c r="F241" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F241" s="23" t="str">
+      <c r="G241" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G241" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H241" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I241" s="26"/>
@@ -29213,7 +29266,7 @@
     <row r="242" ht="36" customHeight="1" spans="1:9">
       <c r="A242" s="19"/>
       <c r="B242" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C242" s="21" t="str">
@@ -29221,23 +29274,23 @@
         <v>[]</v>
       </c>
       <c r="D242" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E242" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E242" s="22" t="str">
+      <c r="F242" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F242" s="23" t="str">
+      <c r="G242" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G242" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H242" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I242" s="26"/>
@@ -29245,7 +29298,7 @@
     <row r="243" ht="36" customHeight="1" spans="1:9">
       <c r="A243" s="19"/>
       <c r="B243" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C243" s="21" t="str">
@@ -29253,23 +29306,23 @@
         <v>[]</v>
       </c>
       <c r="D243" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E243" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E243" s="22" t="str">
+      <c r="F243" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F243" s="23" t="str">
+      <c r="G243" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G243" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H243" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I243" s="26"/>
@@ -29277,7 +29330,7 @@
     <row r="244" ht="36" customHeight="1" spans="1:9">
       <c r="A244" s="19"/>
       <c r="B244" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C244" s="21" t="str">
@@ -29285,23 +29338,23 @@
         <v>[]</v>
       </c>
       <c r="D244" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E244" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E244" s="22" t="str">
+      <c r="F244" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F244" s="23" t="str">
+      <c r="G244" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G244" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H244" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I244" s="26"/>
@@ -29309,7 +29362,7 @@
     <row r="245" ht="36" customHeight="1" spans="1:9">
       <c r="A245" s="19"/>
       <c r="B245" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C245" s="21" t="str">
@@ -29317,23 +29370,23 @@
         <v>[]</v>
       </c>
       <c r="D245" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E245" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E245" s="22" t="str">
+      <c r="F245" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F245" s="23" t="str">
+      <c r="G245" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G245" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H245" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I245" s="26"/>
@@ -29341,7 +29394,7 @@
     <row r="246" ht="36" customHeight="1" spans="1:9">
       <c r="A246" s="19"/>
       <c r="B246" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C246" s="21" t="str">
@@ -29349,23 +29402,23 @@
         <v>[]</v>
       </c>
       <c r="D246" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E246" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E246" s="22" t="str">
+      <c r="F246" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F246" s="23" t="str">
+      <c r="G246" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G246" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H246" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I246" s="26"/>
@@ -29373,7 +29426,7 @@
     <row r="247" ht="36" customHeight="1" spans="1:9">
       <c r="A247" s="19"/>
       <c r="B247" s="20" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="C247" s="21" t="str">
@@ -29381,23 +29434,23 @@
         <v>[]</v>
       </c>
       <c r="D247" s="22" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E247" s="22" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="E247" s="22" t="str">
+      <c r="F247" s="23" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F247" s="23" t="str">
+      <c r="G247" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="G247" s="24" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
       <c r="H247" s="25" t="str">
-        <f ca="1" t="shared" si="38"/>
+        <f ca="1" t="shared" si="37"/>
         <v/>
       </c>
       <c r="I247" s="26"/>
@@ -37451,176 +37504,176 @@
   <sheetData>
     <row r="1" ht="47.25" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="72.75" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" ht="180" customHeight="1" spans="1:3">
       <c r="A5" s="7" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" ht="210" customHeight="1" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" ht="210" customHeight="1" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" ht="255" customHeight="1" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" ht="255" customHeight="1" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" ht="285" customHeight="1" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" ht="285" customHeight="1" spans="1:3">
       <c r="A12" s="7" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" ht="255" customHeight="1" spans="1:3">
       <c r="A13" s="7" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" ht="165" customHeight="1" spans="1:3">
       <c r="A14" s="7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" ht="165" customHeight="1" spans="1:3">
       <c r="A15" s="7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" ht="165" customHeight="1" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" ht="225" customHeight="1" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" ht="180" customHeight="1" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" ht="105" customHeight="1" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" ht="120" customHeight="1" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" ht="135" customHeight="1" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>

--- a/References.xlsx
+++ b/References.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="288">
   <si>
     <t>@article{example2024,   title = {A Reference Example},   journal = {Journal of Examples},   publisher = {Example Press},   author = {Doe, Jane},   year = {2024},   month = aug,   pages = {185–209} }</t>
   </si>
@@ -2915,6 +2915,15 @@
 }</t>
   </si>
   <si>
+    <t>@misc{DOSB2024,
+  author = {{Deutscher Olympischer Sportbund}},
+  title = {{Programmstrategie {Integration durch Sport} 2027--2029}},
+  year = {2024},
+  url = {https://cdn.dosb.de/Relaunch_2024/Integration/Downloads/Programmstrategie_Integration_durch_Sport_2027-2029.pdf},
+  note = {Zugriff am 29. April 2026}
+}</t>
+  </si>
+  <si>
     <t>Bibtex templates</t>
   </si>
   <si>
@@ -27440,34 +27449,36 @@
       <c r="I184" s="26"/>
     </row>
     <row r="185" ht="36" customHeight="1" spans="1:9">
-      <c r="A185" s="19"/>
+      <c r="A185" s="19" t="s">
+        <v>244</v>
+      </c>
       <c r="B185" s="20" t="str">
         <f t="shared" ref="B184:B247" si="38">IFERROR("@"&amp;MID(A185,SEARCH("{",A185)+1,SEARCH(",",A185)-SEARCH("{",A185)-1),"")</f>
-        <v/>
+        <v>@DOSB2024</v>
       </c>
       <c r="C185" s="21" t="str">
         <f t="shared" ref="C185:C248" si="39">"["&amp;B185&amp;"]"</f>
-        <v>[]</v>
+        <v>[@DOSB2024]</v>
       </c>
       <c r="D185" s="22" t="str">
         <f t="shared" si="33"/>
-        <v/>
+        <v>2024</v>
       </c>
       <c r="E185" s="22" t="str">
         <f t="shared" si="34"/>
-        <v/>
+        <v>{Deutscher Olympischer Sportbund</v>
       </c>
       <c r="F185" s="23" t="str">
         <f t="shared" si="35"/>
-        <v/>
+        <v>{Programmstrategie {Integration durch Sport} 2027--2029}</v>
       </c>
       <c r="G185" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="H185" s="25" t="str">
+      <c r="H185" s="25">
         <f ca="1" t="shared" si="37"/>
-        <v/>
+        <v>46141.7755902778</v>
       </c>
       <c r="I185" s="26"/>
     </row>
@@ -37504,176 +37515,176 @@
   <sheetData>
     <row r="1" ht="47.25" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="72.75" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" ht="180" customHeight="1" spans="1:3">
       <c r="A5" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" ht="210" customHeight="1" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" ht="210" customHeight="1" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" ht="255" customHeight="1" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" ht="255" customHeight="1" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" ht="285" customHeight="1" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" ht="285" customHeight="1" spans="1:3">
       <c r="A12" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" ht="255" customHeight="1" spans="1:3">
       <c r="A13" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" ht="165" customHeight="1" spans="1:3">
       <c r="A14" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" ht="165" customHeight="1" spans="1:3">
       <c r="A15" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" ht="165" customHeight="1" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" ht="225" customHeight="1" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" ht="180" customHeight="1" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" ht="105" customHeight="1" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" ht="120" customHeight="1" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" ht="135" customHeight="1" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>

--- a/References.xlsx
+++ b/References.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="290">
   <si>
     <t>@article{example2024,   title = {A Reference Example},   journal = {Journal of Examples},   publisher = {Example Press},   author = {Doe, Jane},   year = {2024},   month = aug,   pages = {185–209} }</t>
   </si>
@@ -2924,6 +2924,34 @@
 }</t>
   </si>
   <si>
+    <t>@article{Domin2021,
+  title = {Smartphone-Based Interventions for Physical Activity Promotion: Scoping Review of the Evidence Over the Last 10 Years},
+  volume = {9},
+  ISSN = {2291-5222},
+  url = {http://dx.doi.org/10.2196/24308},
+  DOI = {10.2196/24308},
+  number = {7},
+  journal = {JMIR mHealth and uHealth},
+  publisher = {JMIR Publications Inc.},
+  author = {Domin,  Alex and Spruijt-Metz,  Donna and Theisen,  Daniel and Ouzzahra,  Yacine and V\"{o}gele,  Claus},
+  year = {2021},
+  month = July,
+  pages = {e24308}
+}</t>
+  </si>
+  <si>
+    <t>@article{Michie2013,
+  author = {Michie, Susan and Richardson, Michelle and Johnston, Marie and Abraham, Charles and Francis, Jill and Hardeman, Wendy and Eccles, Martin P. and Cane, James and Wood, Caroline E.},
+  title = {The behavior change technique taxonomy (v1) of 93 hierarchically clustered techniques: building an international consensus for the reporting of behavior change interventions},
+  journal = {Annals of Behavioral Medicine},
+  volume = {46},
+  number = {1},
+  pages = {81--95},
+  year = {2013},
+  doi = {10.1007/s12160-013-9486-6}
+}</t>
+  </si>
+  <si>
     <t>Bibtex templates</t>
   </si>
   <si>
@@ -27483,66 +27511,70 @@
       <c r="I185" s="26"/>
     </row>
     <row r="186" ht="36" customHeight="1" spans="1:9">
-      <c r="A186" s="19"/>
+      <c r="A186" s="19" t="s">
+        <v>245</v>
+      </c>
       <c r="B186" s="20" t="str">
         <f t="shared" si="38"/>
-        <v/>
+        <v>@Domin2021</v>
       </c>
       <c r="C186" s="21" t="str">
         <f t="shared" si="39"/>
-        <v>[]</v>
+        <v>[@Domin2021]</v>
       </c>
       <c r="D186" s="22" t="str">
         <f t="shared" si="33"/>
-        <v/>
+        <v>2021</v>
       </c>
       <c r="E186" s="22" t="str">
         <f t="shared" si="34"/>
-        <v/>
+        <v>Domin,  Alex and Spruijt-Metz,  Donna and Theisen,  Daniel and Ouzzahra,  Yacine and V\"{o</v>
       </c>
       <c r="F186" s="23" t="str">
         <f t="shared" si="35"/>
-        <v/>
+        <v>Smartphone-Based Interventions for Physical Activity Promotion: Scoping Review of the Evidence Over the Last 10 Years</v>
       </c>
       <c r="G186" s="24" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="H186" s="25" t="str">
+        <v>https://doi.org/10.2196/24308</v>
+      </c>
+      <c r="H186" s="25">
         <f ca="1" t="shared" si="37"/>
-        <v/>
+        <v>46146.7011574074</v>
       </c>
       <c r="I186" s="26"/>
     </row>
     <row r="187" ht="36" customHeight="1" spans="1:9">
-      <c r="A187" s="19"/>
+      <c r="A187" s="19" t="s">
+        <v>246</v>
+      </c>
       <c r="B187" s="20" t="str">
         <f t="shared" si="38"/>
-        <v/>
+        <v>@Michie2013</v>
       </c>
       <c r="C187" s="21" t="str">
         <f t="shared" si="39"/>
-        <v>[]</v>
+        <v>[@Michie2013]</v>
       </c>
       <c r="D187" s="22" t="str">
         <f t="shared" si="33"/>
-        <v/>
+        <v>2013</v>
       </c>
       <c r="E187" s="22" t="str">
         <f t="shared" si="34"/>
-        <v/>
+        <v>Michie, Susan and Richardson, Michelle and Johnston, Marie and Abraham, Charles and Francis, Jill and Hardeman, Wendy and Eccles, Martin P. and Cane, James and Wood, Caroline E.</v>
       </c>
       <c r="F187" s="23" t="str">
         <f t="shared" si="35"/>
-        <v/>
+        <v>The behavior change technique taxonomy (v1) of 93 hierarchically clustered techniques: building an international consensus for the reporting of behavior change interventions</v>
       </c>
       <c r="G187" s="24" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="H187" s="25" t="str">
+        <v>https://doi.org/10.1007/s12160-013-9486-6</v>
+      </c>
+      <c r="H187" s="25">
         <f ca="1" t="shared" si="37"/>
-        <v/>
+        <v>46146.70125</v>
       </c>
       <c r="I187" s="26"/>
     </row>
@@ -37515,176 +37547,176 @@
   <sheetData>
     <row r="1" ht="47.25" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="72.75" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" ht="180" customHeight="1" spans="1:3">
       <c r="A5" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" ht="210" customHeight="1" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" ht="210" customHeight="1" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" ht="255" customHeight="1" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" ht="255" customHeight="1" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" ht="285" customHeight="1" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" ht="285" customHeight="1" spans="1:3">
       <c r="A12" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" ht="255" customHeight="1" spans="1:3">
       <c r="A13" s="7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" ht="165" customHeight="1" spans="1:3">
       <c r="A14" s="7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" ht="165" customHeight="1" spans="1:3">
       <c r="A15" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" ht="165" customHeight="1" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" ht="225" customHeight="1" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" ht="180" customHeight="1" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" ht="105" customHeight="1" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" ht="120" customHeight="1" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" ht="135" customHeight="1" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>

--- a/References.xlsx
+++ b/References.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="293">
   <si>
     <t>@article{example2024,   title = {A Reference Example},   journal = {Journal of Examples},   publisher = {Example Press},   author = {Doe, Jane},   year = {2024},   month = aug,   pages = {185–209} }</t>
   </si>
@@ -2952,6 +2952,52 @@
 }</t>
   </si>
   <si>
+    <t xml:space="preserve"> @article{Wu2023,
+  title = {Comparative effectiveness of school-based exercise interventions on physical fitness in children and adolescents: a systematic review and network meta-analysis},
+  volume = {11},
+  ISSN = {2296-2565},
+  url = {http://dx.doi.org/10.3389/fpubh.2023.1194779},
+  DOI = {10.3389/fpubh.2023.1194779},
+  journal = {Frontiers in Public Health},
+  publisher = {Frontiers Media SA},
+  author = {Wu,  Jin and Yang,  Yuhang and Yu,  Huasen and Li,  Liqiang and Chen,  Yanying and Sun,  Youping},
+  year = {2023},
+  month = June 
+}</t>
+  </si>
+  <si>
+    <t>@article{Kriemler2011,
+  title = {Effect of school-based interventions on physical activity and fitness in children and adolescents: a review of reviews and systematic update},
+  volume = {45},
+  ISSN = {1473-0480},
+  url = {http://dx.doi.org/10.1136/bjsports-2011-090186},
+  DOI = {10.1136/bjsports-2011-090186},
+  number = {11},
+  journal = {British Journal of Sports Medicine},
+  publisher = {BMJ},
+  author = {Kriemler,  S and Meyer,  U and Martin,  E and van Sluijs,  E M F and Andersen,  L B and Martin,  B W},
+  year = {2011},
+  month = Aug,
+  pages = {923–930}
+}</t>
+  </si>
+  <si>
+    <t>@article{Malik2013,
+  title = {A systematic review of workplace health promotion interventions for increasing physical activity},
+  volume = {19},
+  ISSN = {2044-8287},
+  url = {http://dx.doi.org/10.1111/bjhp.12052},
+  DOI = {10.1111/bjhp.12052},
+  number = {1},
+  journal = {British Journal of Health Psychology},
+  publisher = {Wiley},
+  author = {Malik,  Sumaira H. and Blake,  Holly and Suggs,  L. Suzanne},
+  year = {2013},
+  month = July,
+  pages = {149–180}
+}</t>
+  </si>
+  <si>
     <t>Bibtex templates</t>
   </si>
   <si>
@@ -4150,54 +4196,54 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Komma" xfId="1" builtinId="3"/>
-    <cellStyle name="Währung" xfId="2" builtinId="4"/>
-    <cellStyle name="Prozent" xfId="3" builtinId="5"/>
-    <cellStyle name="Komma[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Währung[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Hinweis" xfId="8" builtinId="10"/>
-    <cellStyle name="Warnmeldung" xfId="9" builtinId="11"/>
-    <cellStyle name="Titel" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Überschrift 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Überschrift 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Überschrift 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Überschrift 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Eingabe" xfId="16" builtinId="20"/>
-    <cellStyle name="Ausgabe" xfId="17" builtinId="21"/>
-    <cellStyle name="Berechnung" xfId="18" builtinId="22"/>
-    <cellStyle name="Zelle überprüfen" xfId="19" builtinId="23"/>
-    <cellStyle name="Verknüpfte Zelle" xfId="20" builtinId="24"/>
-    <cellStyle name="Gesamt" xfId="21" builtinId="25"/>
-    <cellStyle name="Gut" xfId="22" builtinId="26"/>
-    <cellStyle name="Schlecht" xfId="23" builtinId="27"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
     <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Akzent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Akzent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Akzent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Akzent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Akzent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Akzent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Akzent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Akzent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Akzent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Akzent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Akzent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Akzent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Akzent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Akzent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Akzent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Akzent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Akzent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Akzent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Akzent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Akzent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Akzent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Akzent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Akzent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Akzent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -27579,98 +27625,104 @@
       <c r="I187" s="26"/>
     </row>
     <row r="188" ht="36" customHeight="1" spans="1:9">
-      <c r="A188" s="19"/>
+      <c r="A188" s="19" t="s">
+        <v>247</v>
+      </c>
       <c r="B188" s="20" t="str">
         <f t="shared" si="38"/>
-        <v/>
+        <v>@Wu2023</v>
       </c>
       <c r="C188" s="21" t="str">
         <f t="shared" si="39"/>
-        <v>[]</v>
+        <v>[@Wu2023]</v>
       </c>
       <c r="D188" s="22" t="str">
         <f t="shared" si="33"/>
-        <v/>
+        <v>2023</v>
       </c>
       <c r="E188" s="22" t="str">
         <f t="shared" si="34"/>
-        <v/>
+        <v>Wu,  Jin and Yang,  Yuhang and Yu,  Huasen and Li,  Liqiang and Chen,  Yanying and Sun,  Youping</v>
       </c>
       <c r="F188" s="23" t="str">
         <f t="shared" si="35"/>
-        <v/>
+        <v>Comparative effectiveness of school-based exercise interventions on physical fitness in children and adolescents: a systematic review and network meta-analysis</v>
       </c>
       <c r="G188" s="24" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="H188" s="25" t="str">
+        <v>https://doi.org/10.3389/fpubh.2023.1194779</v>
+      </c>
+      <c r="H188" s="25">
         <f ca="1" t="shared" si="37"/>
-        <v/>
+        <v>46160.5068171296</v>
       </c>
       <c r="I188" s="26"/>
     </row>
     <row r="189" ht="36" customHeight="1" spans="1:9">
-      <c r="A189" s="19"/>
+      <c r="A189" s="19" t="s">
+        <v>248</v>
+      </c>
       <c r="B189" s="20" t="str">
         <f t="shared" si="38"/>
-        <v/>
+        <v>@Kriemler2011</v>
       </c>
       <c r="C189" s="21" t="str">
         <f t="shared" si="39"/>
-        <v>[]</v>
+        <v>[@Kriemler2011]</v>
       </c>
       <c r="D189" s="22" t="str">
         <f t="shared" si="33"/>
-        <v/>
+        <v>2011</v>
       </c>
       <c r="E189" s="22" t="str">
         <f t="shared" si="34"/>
-        <v/>
+        <v>Kriemler,  S and Meyer,  U and Martin,  E and van Sluijs,  E M F and Andersen,  L B and Martin,  B W</v>
       </c>
       <c r="F189" s="23" t="str">
         <f t="shared" si="35"/>
-        <v/>
+        <v>Effect of school-based interventions on physical activity and fitness in children and adolescents: a review of reviews and systematic update</v>
       </c>
       <c r="G189" s="24" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="H189" s="25" t="str">
+        <v>https://doi.org/10.1136/bjsports-2011-090186</v>
+      </c>
+      <c r="H189" s="25">
         <f ca="1" t="shared" si="37"/>
-        <v/>
+        <v>46160.5074421296</v>
       </c>
       <c r="I189" s="26"/>
     </row>
     <row r="190" ht="36" customHeight="1" spans="1:9">
-      <c r="A190" s="19"/>
+      <c r="A190" s="19" t="s">
+        <v>249</v>
+      </c>
       <c r="B190" s="20" t="str">
         <f t="shared" si="38"/>
-        <v/>
+        <v>@Malik2013</v>
       </c>
       <c r="C190" s="21" t="str">
         <f t="shared" si="39"/>
-        <v>[]</v>
+        <v>[@Malik2013]</v>
       </c>
       <c r="D190" s="22" t="str">
         <f t="shared" si="33"/>
-        <v/>
+        <v>2013</v>
       </c>
       <c r="E190" s="22" t="str">
         <f t="shared" si="34"/>
-        <v/>
+        <v>Malik,  Sumaira H. and Blake,  Holly and Suggs,  L. Suzanne</v>
       </c>
       <c r="F190" s="23" t="str">
         <f t="shared" si="35"/>
-        <v/>
+        <v>A systematic review of workplace health promotion interventions for increasing physical activity</v>
       </c>
       <c r="G190" s="24" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="H190" s="25" t="str">
+        <v>https://doi.org/10.1111/bjhp.12052</v>
+      </c>
+      <c r="H190" s="25">
         <f ca="1" t="shared" si="37"/>
-        <v/>
+        <v>46160.509837963</v>
       </c>
       <c r="I190" s="26"/>
     </row>
@@ -37547,176 +37599,176 @@
   <sheetData>
     <row r="1" ht="47.25" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="72.75" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" ht="180" customHeight="1" spans="1:3">
       <c r="A5" s="7" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" ht="210" customHeight="1" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" ht="210" customHeight="1" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" ht="255" customHeight="1" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" ht="255" customHeight="1" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" ht="285" customHeight="1" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" ht="285" customHeight="1" spans="1:3">
       <c r="A12" s="7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" ht="255" customHeight="1" spans="1:3">
       <c r="A13" s="7" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" ht="165" customHeight="1" spans="1:3">
       <c r="A14" s="7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" ht="165" customHeight="1" spans="1:3">
       <c r="A15" s="7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" ht="165" customHeight="1" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" ht="225" customHeight="1" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" ht="180" customHeight="1" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" ht="105" customHeight="1" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" ht="120" customHeight="1" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" ht="135" customHeight="1" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>

--- a/References.xlsx
+++ b/References.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="DieseArbeitsmappe"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="14400" windowHeight="12255" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Import" sheetId="30" r:id="rId1"/>
@@ -4196,54 +4196,54 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Komma" xfId="1" builtinId="3"/>
+    <cellStyle name="Währung" xfId="2" builtinId="4"/>
+    <cellStyle name="Prozent" xfId="3" builtinId="5"/>
+    <cellStyle name="Komma[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Währung[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Besuchter Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Hinweis" xfId="8" builtinId="10"/>
+    <cellStyle name="Warnmeldung" xfId="9" builtinId="11"/>
+    <cellStyle name="Titel" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Überschrift 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Überschrift 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Überschrift 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Überschrift 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Eingabe" xfId="16" builtinId="20"/>
+    <cellStyle name="Ausgabe" xfId="17" builtinId="21"/>
+    <cellStyle name="Berechnung" xfId="18" builtinId="22"/>
+    <cellStyle name="Zelle überprüfen" xfId="19" builtinId="23"/>
+    <cellStyle name="Verknüpfte Zelle" xfId="20" builtinId="24"/>
+    <cellStyle name="Gesamt" xfId="21" builtinId="25"/>
+    <cellStyle name="Gut" xfId="22" builtinId="26"/>
+    <cellStyle name="Schlecht" xfId="23" builtinId="27"/>
     <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Akzent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Akzent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Akzent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Akzent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Akzent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Akzent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Akzent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Akzent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Akzent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Akzent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Akzent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Akzent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Akzent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Akzent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Akzent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Akzent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Akzent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Akzent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Akzent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Akzent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Akzent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Akzent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Akzent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Akzent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>

--- a/References.xlsx
+++ b/References.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="DieseArbeitsmappe"/>
   <bookViews>
-    <workbookView windowWidth="14400" windowHeight="12255" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12180" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Import" sheetId="30" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="296">
   <si>
     <t>@article{example2024,   title = {A Reference Example},   journal = {Journal of Examples},   publisher = {Example Press},   author = {Doe, Jane},   year = {2024},   month = aug,   pages = {185–209} }</t>
   </si>
@@ -2998,6 +2998,42 @@
 }</t>
   </si>
   <si>
+    <t>@article{westdeutsche_zeitung_schockbilder_2018,
+ author = {{Westdeutsche Zeitung}},
+ title = {Schockbilder schrecken junge Nichtraucher ab},
+ journal = {Westdeutsche Zeitung},
+ year = {2018},
+ date = {2018-05-29},
+ url = {https://www.wz.de/ratgeber/gesundheit-und-ernaehrung/schockbilder-schrecken-junge-nichtraucher-ab_aid-25502279},
+ note = {Zitiert nach einer Online-Quelle (dpa-Meldung). Die genauen Seitenzahlen sind nicht verfügbar.}
+}</t>
+  </si>
+  <si>
+    <t>@article{Wartha2016,
+  title = {Entwicklung eines settingspezifischen Gesundheitsf\"{o}rderprogramms durch die Verwendung des Intervention-Mapping-Ansatzes: „Komm mit in das gesunde Boot –  Kindergarten“},
+  volume = {11},
+  ISSN = {1861-6763},
+  url = {http://dx.doi.org/10.1007/s11553-016-0531-8},
+  DOI = {10.1007/s11553-016-0531-8},
+  number = {2},
+  journal = {Pr\"{a}vention und Gesundheitsf\"{o}rderung},
+  publisher = {Springer Science and Business Media LLC},
+  author = {Wartha,  O. and Kobel,  S. and L\"{a}mmle,  O. and Mosler,  S. and Steinacker,  J M.},
+  year = {2016},
+  month = Mar,
+  pages = {65–72}
+}</t>
+  </si>
+  <si>
+    <t>@misc{znl_komm_mit_2025,
+ author = {{ZNL TransferZentrum für Neurowissenschaften und Lernen, Universität Ulm}},
+ title = {Komm mit in das gesunde Boot: Gesundheitsförderung für Kinder in Krippen, Kindergärten und Grundschulen [Informationsflyer]},
+ year = {2025},
+ url = {https://www.gesundes-boot.de},
+ note = {Das Programm wurde von 2007 bis 2025 von der Baden-Württemberg Stiftung gefördert und wird seit Oktober 2025 von der Techniker Krankenkasse gefördert.}
+}</t>
+  </si>
+  <si>
     <t>Bibtex templates</t>
   </si>
   <si>
@@ -27727,98 +27763,104 @@
       <c r="I190" s="26"/>
     </row>
     <row r="191" ht="36" customHeight="1" spans="1:9">
-      <c r="A191" s="19"/>
+      <c r="A191" s="19" t="s">
+        <v>250</v>
+      </c>
       <c r="B191" s="20" t="str">
         <f t="shared" si="38"/>
-        <v/>
+        <v>@westdeutsche_zeitung_schockbilder_2018</v>
       </c>
       <c r="C191" s="21" t="str">
         <f t="shared" si="39"/>
-        <v>[]</v>
+        <v>[@westdeutsche_zeitung_schockbilder_2018]</v>
       </c>
       <c r="D191" s="22" t="str">
         <f t="shared" si="33"/>
-        <v/>
+        <v>2018</v>
       </c>
       <c r="E191" s="22" t="str">
         <f t="shared" si="34"/>
-        <v/>
+        <v>{Westdeutsche Zeitung</v>
       </c>
       <c r="F191" s="23" t="str">
         <f t="shared" si="35"/>
-        <v/>
+        <v>Schockbilder schrecken junge Nichtraucher ab</v>
       </c>
       <c r="G191" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="H191" s="25" t="str">
+      <c r="H191" s="25">
         <f ca="1" t="shared" si="37"/>
-        <v/>
+        <v>46188.454525463</v>
       </c>
       <c r="I191" s="26"/>
     </row>
     <row r="192" ht="36" customHeight="1" spans="1:9">
-      <c r="A192" s="19"/>
+      <c r="A192" s="19" t="s">
+        <v>251</v>
+      </c>
       <c r="B192" s="20" t="str">
         <f t="shared" si="38"/>
-        <v/>
+        <v>@Wartha2016</v>
       </c>
       <c r="C192" s="21" t="str">
         <f t="shared" si="39"/>
-        <v>[]</v>
+        <v>[@Wartha2016]</v>
       </c>
       <c r="D192" s="22" t="str">
         <f t="shared" si="33"/>
-        <v/>
+        <v>2016</v>
       </c>
       <c r="E192" s="22" t="str">
         <f t="shared" si="34"/>
-        <v/>
+        <v>Wartha,  O. and Kobel,  S. and L\"{a</v>
       </c>
       <c r="F192" s="23" t="str">
         <f t="shared" si="35"/>
-        <v/>
+        <v>Entwicklung eines settingspezifischen Gesundheitsf\"{o}rderprogramms durch die Verwendung des Intervention-Mapping-Ansatzes: „Komm mit in das gesunde Boot –  Kindergarten“</v>
       </c>
       <c r="G192" s="24" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="H192" s="25" t="str">
+        <v>https://doi.org/10.1007/s11553-016-0531-8</v>
+      </c>
+      <c r="H192" s="25">
         <f ca="1" t="shared" si="37"/>
-        <v/>
+        <v>46188.5461458333</v>
       </c>
       <c r="I192" s="26"/>
     </row>
     <row r="193" ht="36" customHeight="1" spans="1:9">
-      <c r="A193" s="19"/>
+      <c r="A193" s="19" t="s">
+        <v>252</v>
+      </c>
       <c r="B193" s="20" t="str">
         <f t="shared" si="38"/>
-        <v/>
+        <v>@znl_komm_mit_2025</v>
       </c>
       <c r="C193" s="21" t="str">
         <f t="shared" si="39"/>
-        <v>[]</v>
+        <v>[@znl_komm_mit_2025]</v>
       </c>
       <c r="D193" s="22" t="str">
         <f t="shared" si="33"/>
-        <v/>
+        <v>2025</v>
       </c>
       <c r="E193" s="22" t="str">
         <f t="shared" si="34"/>
-        <v/>
+        <v>{ZNL TransferZentrum für Neurowissenschaften und Lernen, Universität Ulm</v>
       </c>
       <c r="F193" s="23" t="str">
         <f t="shared" si="35"/>
-        <v/>
+        <v>Komm mit in das gesunde Boot: Gesundheitsförderung für Kinder in Krippen, Kindergärten und Grundschulen [Informationsflyer]</v>
       </c>
       <c r="G193" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="H193" s="25" t="str">
+      <c r="H193" s="25">
         <f ca="1" t="shared" si="37"/>
-        <v/>
+        <v>46188.5497916667</v>
       </c>
       <c r="I193" s="26"/>
     </row>
@@ -37599,176 +37641,176 @@
   <sheetData>
     <row r="1" ht="47.25" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="72.75" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" ht="180" customHeight="1" spans="1:3">
       <c r="A5" s="7" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" ht="210" customHeight="1" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" ht="210" customHeight="1" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" ht="255" customHeight="1" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" ht="255" customHeight="1" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" ht="285" customHeight="1" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" ht="285" customHeight="1" spans="1:3">
       <c r="A12" s="7" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" ht="255" customHeight="1" spans="1:3">
       <c r="A13" s="7" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" ht="165" customHeight="1" spans="1:3">
       <c r="A14" s="7" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" ht="165" customHeight="1" spans="1:3">
       <c r="A15" s="7" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" ht="165" customHeight="1" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" ht="225" customHeight="1" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" ht="180" customHeight="1" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19" ht="105" customHeight="1" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" ht="120" customHeight="1" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" ht="135" customHeight="1" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>

--- a/References.xlsx
+++ b/References.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="297">
   <si>
     <t>@article{example2024,   title = {A Reference Example},   journal = {Journal of Examples},   publisher = {Example Press},   author = {Doe, Jane},   year = {2024},   month = aug,   pages = {185–209} }</t>
   </si>
@@ -3034,6 +3034,18 @@
 }</t>
   </si>
   <si>
+    <t>@book{wartha_komm_mit_2018,
+ author = {Wartha, O. and Kobel, S. and Lämmle, C. and Mosler, S.},
+ title = {Komm mit in das gesunde Boot - Kindergarten: Bewegung, Ernährung und Freizeitgestaltung mit den Inselpiraten},
+ subtitle = {Mit 50 direkt einsetzbaren Bewegungsstunden, Bewegungskartei in praktischer Faltschachtel und Materialien für die Elternarbeit},
+ year = {2018},
+ publisher = {Auer Verlag},
+ address = {Augsburg},
+ isbn = {978-3-403-07718-3},
+ note = {Ordner, 200 Seiten, DIN A4, Vorschule &amp; KiTa, Best.-Nr. 07718}
+}</t>
+  </si>
+  <si>
     <t>Bibtex templates</t>
   </si>
   <si>
@@ -27865,34 +27877,36 @@
       <c r="I193" s="26"/>
     </row>
     <row r="194" ht="36" customHeight="1" spans="1:9">
-      <c r="A194" s="19"/>
+      <c r="A194" s="19" t="s">
+        <v>253</v>
+      </c>
       <c r="B194" s="20" t="str">
         <f t="shared" si="38"/>
-        <v/>
+        <v>@wartha_komm_mit_2018</v>
       </c>
       <c r="C194" s="21" t="str">
         <f t="shared" si="39"/>
-        <v>[]</v>
+        <v>[@wartha_komm_mit_2018]</v>
       </c>
       <c r="D194" s="22" t="str">
         <f t="shared" si="33"/>
-        <v/>
+        <v>2018</v>
       </c>
       <c r="E194" s="22" t="str">
         <f t="shared" si="34"/>
-        <v/>
+        <v>Wartha, O. and Kobel, S. and Lämmle, C. and Mosler, S.</v>
       </c>
       <c r="F194" s="23" t="str">
         <f t="shared" si="35"/>
-        <v/>
+        <v>Komm mit in das gesunde Boot - Kindergarten: Bewegung, Ernährung und Freizeitgestaltung mit den Inselpiraten</v>
       </c>
       <c r="G194" s="24" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="H194" s="25" t="str">
+      <c r="H194" s="25">
         <f ca="1" t="shared" si="37"/>
-        <v/>
+        <v>46193.439537037</v>
       </c>
       <c r="I194" s="26"/>
     </row>
@@ -37641,176 +37655,176 @@
   <sheetData>
     <row r="1" ht="47.25" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="72.75" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" ht="180" customHeight="1" spans="1:3">
       <c r="A5" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" ht="210" customHeight="1" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" ht="210" customHeight="1" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" ht="255" customHeight="1" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" ht="255" customHeight="1" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" ht="285" customHeight="1" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" ht="285" customHeight="1" spans="1:3">
       <c r="A12" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" ht="255" customHeight="1" spans="1:3">
       <c r="A13" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" ht="165" customHeight="1" spans="1:3">
       <c r="A14" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" ht="165" customHeight="1" spans="1:3">
       <c r="A15" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" ht="165" customHeight="1" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" ht="225" customHeight="1" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18" ht="180" customHeight="1" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" ht="105" customHeight="1" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" ht="120" customHeight="1" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="21" ht="135" customHeight="1" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
